--- a/AAII_Financials/Yearly/MOR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MOR_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,49 +656,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -708,29 +708,32 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>301900</v>
+        <v>259300</v>
       </c>
       <c r="E8" s="3">
-        <v>194900</v>
+        <v>302800</v>
       </c>
       <c r="F8" s="3">
-        <v>355600</v>
+        <v>195400</v>
       </c>
       <c r="G8" s="3">
-        <v>77900</v>
+        <v>356600</v>
       </c>
       <c r="H8" s="3">
-        <v>82900</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
+        <v>78100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>83200</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -741,29 +744,32 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>52800</v>
+        <v>55400</v>
       </c>
       <c r="E9" s="3">
-        <v>34900</v>
+        <v>52900</v>
       </c>
       <c r="F9" s="3">
-        <v>20700</v>
+        <v>35000</v>
       </c>
       <c r="G9" s="3">
+        <v>20800</v>
+      </c>
+      <c r="H9" s="3">
         <v>3700</v>
       </c>
-      <c r="H9" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+      <c r="I9" s="3">
+        <v>2000</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -774,29 +780,32 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>249200</v>
+        <v>203800</v>
       </c>
       <c r="E10" s="3">
-        <v>159900</v>
+        <v>249900</v>
       </c>
       <c r="F10" s="3">
-        <v>334800</v>
+        <v>160400</v>
       </c>
       <c r="G10" s="3">
-        <v>74200</v>
+        <v>335800</v>
       </c>
       <c r="H10" s="3">
-        <v>81000</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+        <v>74400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>81200</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -807,9 +816,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,28 +835,29 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>308700</v>
+        <v>290100</v>
       </c>
       <c r="E12" s="3">
-        <v>237700</v>
+        <v>309600</v>
       </c>
       <c r="F12" s="3">
-        <v>130700</v>
+        <v>238400</v>
       </c>
       <c r="G12" s="3">
-        <v>112700</v>
+        <v>131100</v>
       </c>
       <c r="H12" s="3">
-        <v>91100</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
+        <v>113000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>91400</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
@@ -855,9 +868,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,29 +904,32 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E14" s="3">
         <v>9000</v>
       </c>
-      <c r="E14" s="3">
-        <v>251700</v>
-      </c>
       <c r="F14" s="3">
+        <v>252400</v>
+      </c>
+      <c r="G14" s="3">
         <v>7400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>10300</v>
       </c>
-      <c r="H14" s="3">
-        <v>21900</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>22000</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -921,30 +940,33 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E15" s="3">
         <v>8400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4100</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
@@ -954,9 +976,12 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,28 +992,29 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>545300</v>
+        <v>535800</v>
       </c>
       <c r="E17" s="3">
-        <v>744100</v>
+        <v>546900</v>
       </c>
       <c r="F17" s="3">
-        <v>326600</v>
+        <v>746200</v>
       </c>
       <c r="G17" s="3">
-        <v>194000</v>
+        <v>327600</v>
       </c>
       <c r="H17" s="3">
-        <v>148200</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
+        <v>194600</v>
+      </c>
+      <c r="I17" s="3">
+        <v>148600</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -999,29 +1025,32 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-243400</v>
+        <v>-276500</v>
       </c>
       <c r="E18" s="3">
-        <v>-549200</v>
+        <v>-244100</v>
       </c>
       <c r="F18" s="3">
-        <v>28900</v>
+        <v>-550800</v>
       </c>
       <c r="G18" s="3">
-        <v>-116100</v>
+        <v>29000</v>
       </c>
       <c r="H18" s="3">
-        <v>-65300</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
+        <v>-116500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-65400</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1032,9 +1061,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,29 +1080,30 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>387000</v>
+        <v>188300</v>
       </c>
       <c r="E20" s="3">
-        <v>-20600</v>
+        <v>388100</v>
       </c>
       <c r="F20" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,29 +1113,32 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>155000</v>
+        <v>-76700</v>
       </c>
       <c r="E21" s="3">
-        <v>-558900</v>
+        <v>155500</v>
       </c>
       <c r="F21" s="3">
-        <v>37400</v>
+        <v>-560500</v>
       </c>
       <c r="G21" s="3">
-        <v>-107800</v>
+        <v>37500</v>
       </c>
       <c r="H21" s="3">
-        <v>-61400</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
+        <v>-108100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-61600</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1113,30 +1149,33 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>124600</v>
+        <v>119500</v>
       </c>
       <c r="E22" s="3">
-        <v>71400</v>
+        <v>124900</v>
       </c>
       <c r="F22" s="3">
+        <v>71600</v>
+      </c>
+      <c r="G22" s="3">
         <v>3900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1146,29 +1185,32 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>19000</v>
+        <v>-207700</v>
       </c>
       <c r="E23" s="3">
-        <v>-641300</v>
+        <v>19100</v>
       </c>
       <c r="F23" s="3">
-        <v>24400</v>
+        <v>-643100</v>
       </c>
       <c r="G23" s="3">
-        <v>-115600</v>
+        <v>24500</v>
       </c>
       <c r="H23" s="3">
-        <v>-65600</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
+        <v>-115900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-65800</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1179,30 +1221,33 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>182900</v>
+        <v>-1300</v>
       </c>
       <c r="E24" s="3">
-        <v>-83100</v>
+        <v>183400</v>
       </c>
       <c r="F24" s="3">
-        <v>-81800</v>
+        <v>-83300</v>
       </c>
       <c r="G24" s="3">
+        <v>-82000</v>
+      </c>
+      <c r="H24" s="3">
         <v>-3800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4700</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1212,9 +1257,12 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,29 +1293,32 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-163900</v>
+        <v>-206400</v>
       </c>
       <c r="E26" s="3">
-        <v>-558200</v>
+        <v>-164400</v>
       </c>
       <c r="F26" s="3">
-        <v>106200</v>
+        <v>-559800</v>
       </c>
       <c r="G26" s="3">
-        <v>-111800</v>
+        <v>106500</v>
       </c>
       <c r="H26" s="3">
-        <v>-60900</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
+        <v>-112100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-61100</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
@@ -1278,29 +1329,32 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-163900</v>
+        <v>-206400</v>
       </c>
       <c r="E27" s="3">
-        <v>-558200</v>
+        <v>-164400</v>
       </c>
       <c r="F27" s="3">
-        <v>106200</v>
+        <v>-559800</v>
       </c>
       <c r="G27" s="3">
-        <v>-111800</v>
+        <v>106500</v>
       </c>
       <c r="H27" s="3">
-        <v>-60900</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
+        <v>-112100</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-61100</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1311,9 +1365,12 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,30 +1509,33 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-387000</v>
+        <v>-188300</v>
       </c>
       <c r="E32" s="3">
-        <v>20600</v>
+        <v>-388100</v>
       </c>
       <c r="F32" s="3">
+        <v>20700</v>
+      </c>
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1476,29 +1545,32 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-163900</v>
+        <v>-206400</v>
       </c>
       <c r="E33" s="3">
-        <v>-558200</v>
+        <v>-164400</v>
       </c>
       <c r="F33" s="3">
-        <v>106200</v>
+        <v>-559800</v>
       </c>
       <c r="G33" s="3">
-        <v>-111800</v>
+        <v>106500</v>
       </c>
       <c r="H33" s="3">
-        <v>-60900</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
+        <v>-112100</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-61100</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
@@ -1509,9 +1581,12 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,29 +1617,32 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-163900</v>
+        <v>-206400</v>
       </c>
       <c r="E35" s="3">
-        <v>-558200</v>
+        <v>-164400</v>
       </c>
       <c r="F35" s="3">
-        <v>106200</v>
+        <v>-559800</v>
       </c>
       <c r="G35" s="3">
-        <v>-111800</v>
+        <v>106500</v>
       </c>
       <c r="H35" s="3">
-        <v>-60900</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
+        <v>-112100</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-61100</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
@@ -1575,35 +1653,38 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1613,9 +1694,12 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,28 +1729,29 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>436600</v>
+        <v>172500</v>
       </c>
       <c r="E41" s="3">
-        <v>133700</v>
+        <v>437800</v>
       </c>
       <c r="F41" s="3">
-        <v>119100</v>
+        <v>134100</v>
       </c>
       <c r="G41" s="3">
-        <v>48100</v>
+        <v>119500</v>
       </c>
       <c r="H41" s="3">
-        <v>49300</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
+        <v>48200</v>
+      </c>
+      <c r="I41" s="3">
+        <v>49500</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
@@ -1676,29 +1762,32 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>547700</v>
+        <v>570400</v>
       </c>
       <c r="E42" s="3">
-        <v>944400</v>
+        <v>549300</v>
       </c>
       <c r="F42" s="3">
-        <v>1063900</v>
+        <v>947100</v>
       </c>
       <c r="G42" s="3">
-        <v>247600</v>
+        <v>1066900</v>
       </c>
       <c r="H42" s="3">
-        <v>340200</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
+        <v>248300</v>
+      </c>
+      <c r="I42" s="3">
+        <v>341100</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
@@ -1709,29 +1798,32 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>121900</v>
+        <v>46400</v>
       </c>
       <c r="E43" s="3">
-        <v>93100</v>
+        <v>122300</v>
       </c>
       <c r="F43" s="3">
-        <v>97500</v>
+        <v>93300</v>
       </c>
       <c r="G43" s="3">
+        <v>97800</v>
+      </c>
+      <c r="H43" s="3">
         <v>22100</v>
       </c>
-      <c r="H43" s="3">
-        <v>22500</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
+      <c r="I43" s="3">
+        <v>22600</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -1742,29 +1834,32 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>26300</v>
+        <v>67500</v>
       </c>
       <c r="E44" s="3">
-        <v>22500</v>
+        <v>26400</v>
       </c>
       <c r="F44" s="3">
+        <v>22600</v>
+      </c>
+      <c r="G44" s="3">
         <v>10800</v>
-      </c>
-      <c r="G44" s="3">
-        <v>300</v>
       </c>
       <c r="H44" s="3">
         <v>300</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
+      <c r="I44" s="3">
+        <v>300</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -1775,30 +1870,33 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>49100</v>
+        <v>28900</v>
       </c>
       <c r="E45" s="3">
-        <v>35500</v>
+        <v>49200</v>
       </c>
       <c r="F45" s="3">
-        <v>18100</v>
+        <v>35600</v>
       </c>
       <c r="G45" s="3">
+        <v>18200</v>
+      </c>
+      <c r="H45" s="3">
         <v>11500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9700</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,29 +1906,32 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1181600</v>
+        <v>885700</v>
       </c>
       <c r="E46" s="3">
-        <v>1229300</v>
+        <v>1185000</v>
       </c>
       <c r="F46" s="3">
-        <v>1309400</v>
+        <v>1232800</v>
       </c>
       <c r="G46" s="3">
-        <v>329500</v>
+        <v>1313100</v>
       </c>
       <c r="H46" s="3">
-        <v>422000</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
+        <v>330400</v>
+      </c>
+      <c r="I46" s="3">
+        <v>423200</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
@@ -1841,29 +1942,32 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E47" s="3">
         <v>5800</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
       <c r="F47" s="3">
-        <v>213300</v>
+        <v>0</v>
       </c>
       <c r="G47" s="3">
-        <v>107400</v>
+        <v>213900</v>
       </c>
       <c r="H47" s="3">
-        <v>104100</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
+        <v>107700</v>
+      </c>
+      <c r="I47" s="3">
+        <v>104400</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
@@ -1874,30 +1978,33 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>55300</v>
+        <v>16300</v>
       </c>
       <c r="E48" s="3">
-        <v>53800</v>
+        <v>55500</v>
       </c>
       <c r="F48" s="3">
-        <v>55100</v>
+        <v>54000</v>
       </c>
       <c r="G48" s="3">
-        <v>51900</v>
+        <v>55200</v>
       </c>
       <c r="H48" s="3">
+        <v>52000</v>
+      </c>
+      <c r="I48" s="3">
         <v>3800</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1907,29 +2014,32 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1348500</v>
+        <v>1290900</v>
       </c>
       <c r="E49" s="3">
-        <v>1273700</v>
+        <v>1352300</v>
       </c>
       <c r="F49" s="3">
-        <v>77000</v>
+        <v>1277300</v>
       </c>
       <c r="G49" s="3">
-        <v>48600</v>
+        <v>77200</v>
       </c>
       <c r="H49" s="3">
-        <v>51400</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+        <v>48700</v>
+      </c>
+      <c r="I49" s="3">
+        <v>51500</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -1940,9 +2050,12 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,30 +2122,33 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E52" s="3">
         <v>9500</v>
       </c>
-      <c r="E52" s="3">
-        <v>216800</v>
-      </c>
       <c r="F52" s="3">
-        <v>145800</v>
+        <v>217400</v>
       </c>
       <c r="G52" s="3">
+        <v>146200</v>
+      </c>
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3200</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2039,9 +2158,12 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,29 +2194,32 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2600700</v>
+        <v>2204800</v>
       </c>
       <c r="E54" s="3">
-        <v>2773500</v>
+        <v>2608100</v>
       </c>
       <c r="F54" s="3">
-        <v>1800600</v>
+        <v>2781500</v>
       </c>
       <c r="G54" s="3">
-        <v>538600</v>
+        <v>1805700</v>
       </c>
       <c r="H54" s="3">
-        <v>584600</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
+        <v>540200</v>
+      </c>
+      <c r="I54" s="3">
+        <v>586200</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
@@ -2105,9 +2230,12 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,28 +2265,29 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>41900</v>
+        <v>30900</v>
       </c>
       <c r="E57" s="3">
-        <v>80100</v>
+        <v>42000</v>
       </c>
       <c r="F57" s="3">
-        <v>51900</v>
+        <v>80300</v>
       </c>
       <c r="G57" s="3">
-        <v>11900</v>
+        <v>52000</v>
       </c>
       <c r="H57" s="3">
-        <v>8000</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
+        <v>12000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>8100</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -2168,26 +2298,29 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E58" s="3">
         <v>10400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3800</v>
       </c>
-      <c r="G58" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>2800</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2201,29 +2334,32 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>249700</v>
+        <v>251000</v>
       </c>
       <c r="E59" s="3">
-        <v>224700</v>
+        <v>250500</v>
       </c>
       <c r="F59" s="3">
-        <v>161800</v>
+        <v>225300</v>
       </c>
       <c r="G59" s="3">
-        <v>52100</v>
+        <v>162300</v>
       </c>
       <c r="H59" s="3">
-        <v>41800</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
+        <v>52200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>41900</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2234,29 +2370,32 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>302000</v>
+        <v>287600</v>
       </c>
       <c r="E60" s="3">
-        <v>308700</v>
+        <v>302900</v>
       </c>
       <c r="F60" s="3">
-        <v>217500</v>
+        <v>309600</v>
       </c>
       <c r="G60" s="3">
-        <v>66800</v>
+        <v>218100</v>
       </c>
       <c r="H60" s="3">
-        <v>49800</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
+        <v>67000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>50000</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
@@ -2267,30 +2406,33 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>357900</v>
+        <v>275100</v>
       </c>
       <c r="E61" s="3">
-        <v>349500</v>
+        <v>358900</v>
       </c>
       <c r="F61" s="3">
-        <v>341500</v>
+        <v>350500</v>
       </c>
       <c r="G61" s="3">
-        <v>43400</v>
+        <v>342500</v>
       </c>
       <c r="H61" s="3">
+        <v>43600</v>
+      </c>
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2300,30 +2442,33 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1770000</v>
+        <v>1588800</v>
       </c>
       <c r="E62" s="3">
-        <v>1849600</v>
+        <v>1775000</v>
       </c>
       <c r="F62" s="3">
-        <v>567500</v>
+        <v>1854900</v>
       </c>
       <c r="G62" s="3">
-        <v>100</v>
+        <v>569100</v>
       </c>
       <c r="H62" s="3">
+        <v>200</v>
+      </c>
+      <c r="I62" s="3">
         <v>4800</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,9 +2478,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,29 +2586,32 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2429900</v>
+        <v>2151500</v>
       </c>
       <c r="E66" s="3">
-        <v>2507800</v>
+        <v>2436800</v>
       </c>
       <c r="F66" s="3">
-        <v>1126400</v>
+        <v>2515000</v>
       </c>
       <c r="G66" s="3">
-        <v>110400</v>
+        <v>1129700</v>
       </c>
       <c r="H66" s="3">
-        <v>54700</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
+        <v>110700</v>
+      </c>
+      <c r="I66" s="3">
+        <v>54800</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2465,9 +2622,12 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,29 +2782,32 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-893400</v>
+        <v>-1102400</v>
       </c>
       <c r="E72" s="3">
-        <v>-729500</v>
+        <v>-895900</v>
       </c>
       <c r="F72" s="3">
-        <v>-171300</v>
+        <v>-731600</v>
       </c>
       <c r="G72" s="3">
-        <v>-277500</v>
+        <v>-171800</v>
       </c>
       <c r="H72" s="3">
-        <v>-165800</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
+        <v>-278300</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-166200</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2645,9 +2818,12 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,29 +2926,32 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>170800</v>
+        <v>53400</v>
       </c>
       <c r="E76" s="3">
-        <v>265700</v>
+        <v>171300</v>
       </c>
       <c r="F76" s="3">
-        <v>674100</v>
+        <v>266400</v>
       </c>
       <c r="G76" s="3">
-        <v>428300</v>
+        <v>676100</v>
       </c>
       <c r="H76" s="3">
-        <v>529900</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
+        <v>429500</v>
+      </c>
+      <c r="I76" s="3">
+        <v>531400</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -2777,9 +2962,12 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,35 +2998,38 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2848,29 +3039,32 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-163900</v>
+        <v>-206400</v>
       </c>
       <c r="E81" s="3">
-        <v>-558200</v>
+        <v>-164400</v>
       </c>
       <c r="F81" s="3">
-        <v>106200</v>
+        <v>-559800</v>
       </c>
       <c r="G81" s="3">
-        <v>-111800</v>
+        <v>106500</v>
       </c>
       <c r="H81" s="3">
-        <v>-60900</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
+        <v>-112100</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-61100</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
@@ -2881,9 +3075,12 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,29 +3094,30 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11400</v>
+        <v>11500</v>
       </c>
       <c r="E83" s="3">
-        <v>10900</v>
+        <v>11500</v>
       </c>
       <c r="F83" s="3">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="G83" s="3">
+        <v>9100</v>
+      </c>
+      <c r="H83" s="3">
         <v>6800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4100</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,9 +3127,12 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,29 +3307,32 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-397900</v>
+        <v>-321900</v>
       </c>
       <c r="E89" s="3">
-        <v>-522400</v>
+        <v>-399000</v>
       </c>
       <c r="F89" s="3">
-        <v>37500</v>
+        <v>-523900</v>
       </c>
       <c r="G89" s="3">
-        <v>-88000</v>
+        <v>37600</v>
       </c>
       <c r="H89" s="3">
-        <v>-35600</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+        <v>-88200</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-35700</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -3127,9 +3343,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,29 +3362,30 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,9 +3395,12 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,29 +3467,32 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>374300</v>
+        <v>16700</v>
       </c>
       <c r="E94" s="3">
-        <v>-901600</v>
+        <v>375400</v>
       </c>
       <c r="F94" s="3">
-        <v>-954400</v>
+        <v>-904200</v>
       </c>
       <c r="G94" s="3">
-        <v>86200</v>
+        <v>-957100</v>
       </c>
       <c r="H94" s="3">
-        <v>-192900</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+        <v>86500</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-193400</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
@@ -3274,9 +3503,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,8 +3522,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,29 +3663,32 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>337900</v>
+        <v>46800</v>
       </c>
       <c r="E100" s="3">
-        <v>1435400</v>
+        <v>338900</v>
       </c>
       <c r="F100" s="3">
-        <v>984300</v>
+        <v>1439500</v>
       </c>
       <c r="G100" s="3">
+        <v>987100</v>
+      </c>
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
-        <v>194700</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+      <c r="I100" s="3">
+        <v>195300</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
@@ -3454,30 +3699,33 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-11500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3487,29 +3735,32 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>302800</v>
+        <v>-265300</v>
       </c>
       <c r="E102" s="3">
+        <v>303700</v>
+      </c>
+      <c r="F102" s="3">
         <v>14600</v>
       </c>
-      <c r="F102" s="3">
-        <v>71000</v>
-      </c>
       <c r="G102" s="3">
+        <v>71200</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1200</v>
       </c>
-      <c r="H102" s="3">
-        <v>-33800</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
+      <c r="I102" s="3">
+        <v>-33900</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
@@ -3520,7 +3771,10 @@
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MOR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MOR_YR_FIN.xlsx
@@ -718,22 +718,22 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>259300</v>
+        <v>257500</v>
       </c>
       <c r="E8" s="3">
-        <v>302800</v>
+        <v>300700</v>
       </c>
       <c r="F8" s="3">
-        <v>195400</v>
+        <v>194100</v>
       </c>
       <c r="G8" s="3">
-        <v>356600</v>
+        <v>354100</v>
       </c>
       <c r="H8" s="3">
-        <v>78100</v>
+        <v>77500</v>
       </c>
       <c r="I8" s="3">
-        <v>83200</v>
+        <v>82600</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -754,22 +754,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>55400</v>
+        <v>55100</v>
       </c>
       <c r="E9" s="3">
-        <v>52900</v>
+        <v>52500</v>
       </c>
       <c r="F9" s="3">
-        <v>35000</v>
+        <v>34800</v>
       </c>
       <c r="G9" s="3">
-        <v>20800</v>
+        <v>20600</v>
       </c>
       <c r="H9" s="3">
         <v>3700</v>
       </c>
       <c r="I9" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -790,22 +790,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>203800</v>
+        <v>202400</v>
       </c>
       <c r="E10" s="3">
-        <v>249900</v>
+        <v>248200</v>
       </c>
       <c r="F10" s="3">
-        <v>160400</v>
+        <v>159300</v>
       </c>
       <c r="G10" s="3">
-        <v>335800</v>
+        <v>333500</v>
       </c>
       <c r="H10" s="3">
-        <v>74400</v>
+        <v>73900</v>
       </c>
       <c r="I10" s="3">
-        <v>81200</v>
+        <v>80700</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -842,22 +842,22 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>290100</v>
+        <v>288200</v>
       </c>
       <c r="E12" s="3">
-        <v>309600</v>
+        <v>307500</v>
       </c>
       <c r="F12" s="3">
-        <v>238400</v>
+        <v>236800</v>
       </c>
       <c r="G12" s="3">
-        <v>131100</v>
+        <v>130200</v>
       </c>
       <c r="H12" s="3">
-        <v>113000</v>
+        <v>112200</v>
       </c>
       <c r="I12" s="3">
-        <v>91400</v>
+        <v>90800</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
@@ -914,22 +914,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>19700</v>
+        <v>19600</v>
       </c>
       <c r="E14" s="3">
         <v>9000</v>
       </c>
       <c r="F14" s="3">
-        <v>252400</v>
+        <v>250700</v>
       </c>
       <c r="G14" s="3">
-        <v>7400</v>
+        <v>7300</v>
       </c>
       <c r="H14" s="3">
-        <v>10300</v>
+        <v>10200</v>
       </c>
       <c r="I14" s="3">
-        <v>22000</v>
+        <v>21900</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -950,7 +950,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>11700</v>
+        <v>11600</v>
       </c>
       <c r="E15" s="3">
         <v>8400</v>
@@ -959,10 +959,10 @@
         <v>8200</v>
       </c>
       <c r="G15" s="3">
-        <v>7900</v>
+        <v>7800</v>
       </c>
       <c r="H15" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="I15" s="3">
         <v>4100</v>
@@ -999,22 +999,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>535800</v>
+        <v>532100</v>
       </c>
       <c r="E17" s="3">
-        <v>546900</v>
+        <v>543200</v>
       </c>
       <c r="F17" s="3">
-        <v>746200</v>
+        <v>741200</v>
       </c>
       <c r="G17" s="3">
-        <v>327600</v>
+        <v>325300</v>
       </c>
       <c r="H17" s="3">
-        <v>194600</v>
+        <v>193200</v>
       </c>
       <c r="I17" s="3">
-        <v>148600</v>
+        <v>147600</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -1035,22 +1035,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-276500</v>
+        <v>-274600</v>
       </c>
       <c r="E18" s="3">
-        <v>-244100</v>
+        <v>-242400</v>
       </c>
       <c r="F18" s="3">
-        <v>-550800</v>
+        <v>-547100</v>
       </c>
       <c r="G18" s="3">
-        <v>29000</v>
+        <v>28800</v>
       </c>
       <c r="H18" s="3">
-        <v>-116500</v>
+        <v>-115700</v>
       </c>
       <c r="I18" s="3">
-        <v>-65400</v>
+        <v>-65000</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1087,13 +1087,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>188300</v>
+        <v>187000</v>
       </c>
       <c r="E20" s="3">
-        <v>388100</v>
+        <v>385500</v>
       </c>
       <c r="F20" s="3">
-        <v>-20700</v>
+        <v>-20600</v>
       </c>
       <c r="G20" s="3">
         <v>-600</v>
@@ -1123,22 +1123,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-76700</v>
+        <v>-76300</v>
       </c>
       <c r="E21" s="3">
-        <v>155500</v>
+        <v>154300</v>
       </c>
       <c r="F21" s="3">
-        <v>-560500</v>
+        <v>-556800</v>
       </c>
       <c r="G21" s="3">
-        <v>37500</v>
+        <v>37200</v>
       </c>
       <c r="H21" s="3">
-        <v>-108100</v>
+        <v>-107400</v>
       </c>
       <c r="I21" s="3">
-        <v>-61600</v>
+        <v>-61200</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1159,13 +1159,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>119500</v>
+        <v>118700</v>
       </c>
       <c r="E22" s="3">
-        <v>124900</v>
+        <v>124100</v>
       </c>
       <c r="F22" s="3">
-        <v>71600</v>
+        <v>71100</v>
       </c>
       <c r="G22" s="3">
         <v>3900</v>
@@ -1195,22 +1195,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-207700</v>
+        <v>-206300</v>
       </c>
       <c r="E23" s="3">
-        <v>19100</v>
+        <v>18900</v>
       </c>
       <c r="F23" s="3">
-        <v>-643100</v>
+        <v>-638700</v>
       </c>
       <c r="G23" s="3">
-        <v>24500</v>
+        <v>24300</v>
       </c>
       <c r="H23" s="3">
-        <v>-115900</v>
+        <v>-115100</v>
       </c>
       <c r="I23" s="3">
-        <v>-65800</v>
+        <v>-65400</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1234,13 +1234,13 @@
         <v>-1300</v>
       </c>
       <c r="E24" s="3">
-        <v>183400</v>
+        <v>182200</v>
       </c>
       <c r="F24" s="3">
-        <v>-83300</v>
+        <v>-82800</v>
       </c>
       <c r="G24" s="3">
-        <v>-82000</v>
+        <v>-81500</v>
       </c>
       <c r="H24" s="3">
         <v>-3800</v>
@@ -1303,22 +1303,22 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-206400</v>
+        <v>-205000</v>
       </c>
       <c r="E26" s="3">
-        <v>-164400</v>
+        <v>-163200</v>
       </c>
       <c r="F26" s="3">
-        <v>-559800</v>
+        <v>-556000</v>
       </c>
       <c r="G26" s="3">
-        <v>106500</v>
+        <v>105800</v>
       </c>
       <c r="H26" s="3">
-        <v>-112100</v>
+        <v>-111300</v>
       </c>
       <c r="I26" s="3">
-        <v>-61100</v>
+        <v>-60700</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
@@ -1339,22 +1339,22 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-206400</v>
+        <v>-205000</v>
       </c>
       <c r="E27" s="3">
-        <v>-164400</v>
+        <v>-163200</v>
       </c>
       <c r="F27" s="3">
-        <v>-559800</v>
+        <v>-556000</v>
       </c>
       <c r="G27" s="3">
-        <v>106500</v>
+        <v>105800</v>
       </c>
       <c r="H27" s="3">
-        <v>-112100</v>
+        <v>-111300</v>
       </c>
       <c r="I27" s="3">
-        <v>-61100</v>
+        <v>-60700</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1519,13 +1519,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-188300</v>
+        <v>-187000</v>
       </c>
       <c r="E32" s="3">
-        <v>-388100</v>
+        <v>-385500</v>
       </c>
       <c r="F32" s="3">
-        <v>20700</v>
+        <v>20600</v>
       </c>
       <c r="G32" s="3">
         <v>600</v>
@@ -1555,22 +1555,22 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-206400</v>
+        <v>-205000</v>
       </c>
       <c r="E33" s="3">
-        <v>-164400</v>
+        <v>-163200</v>
       </c>
       <c r="F33" s="3">
-        <v>-559800</v>
+        <v>-556000</v>
       </c>
       <c r="G33" s="3">
-        <v>106500</v>
+        <v>105800</v>
       </c>
       <c r="H33" s="3">
-        <v>-112100</v>
+        <v>-111300</v>
       </c>
       <c r="I33" s="3">
-        <v>-61100</v>
+        <v>-60700</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
@@ -1627,22 +1627,22 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-206400</v>
+        <v>-205000</v>
       </c>
       <c r="E35" s="3">
-        <v>-164400</v>
+        <v>-163200</v>
       </c>
       <c r="F35" s="3">
-        <v>-559800</v>
+        <v>-556000</v>
       </c>
       <c r="G35" s="3">
-        <v>106500</v>
+        <v>105800</v>
       </c>
       <c r="H35" s="3">
-        <v>-112100</v>
+        <v>-111300</v>
       </c>
       <c r="I35" s="3">
-        <v>-61100</v>
+        <v>-60700</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
@@ -1736,22 +1736,22 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>172500</v>
+        <v>171300</v>
       </c>
       <c r="E41" s="3">
-        <v>437800</v>
+        <v>434800</v>
       </c>
       <c r="F41" s="3">
-        <v>134100</v>
+        <v>133200</v>
       </c>
       <c r="G41" s="3">
-        <v>119500</v>
+        <v>118700</v>
       </c>
       <c r="H41" s="3">
-        <v>48200</v>
+        <v>47900</v>
       </c>
       <c r="I41" s="3">
-        <v>49500</v>
+        <v>49100</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
@@ -1772,22 +1772,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>570400</v>
+        <v>566600</v>
       </c>
       <c r="E42" s="3">
-        <v>549300</v>
+        <v>545600</v>
       </c>
       <c r="F42" s="3">
-        <v>947100</v>
+        <v>940700</v>
       </c>
       <c r="G42" s="3">
-        <v>1066900</v>
+        <v>1059600</v>
       </c>
       <c r="H42" s="3">
-        <v>248300</v>
+        <v>246600</v>
       </c>
       <c r="I42" s="3">
-        <v>341100</v>
+        <v>338800</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
@@ -1808,22 +1808,22 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>46400</v>
+        <v>46100</v>
       </c>
       <c r="E43" s="3">
-        <v>122300</v>
+        <v>121400</v>
       </c>
       <c r="F43" s="3">
-        <v>93300</v>
+        <v>92700</v>
       </c>
       <c r="G43" s="3">
-        <v>97800</v>
+        <v>97100</v>
       </c>
       <c r="H43" s="3">
-        <v>22100</v>
+        <v>22000</v>
       </c>
       <c r="I43" s="3">
-        <v>22600</v>
+        <v>22400</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -1844,13 +1844,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>67500</v>
+        <v>67100</v>
       </c>
       <c r="E44" s="3">
-        <v>26400</v>
+        <v>26200</v>
       </c>
       <c r="F44" s="3">
-        <v>22600</v>
+        <v>22400</v>
       </c>
       <c r="G44" s="3">
         <v>10800</v>
@@ -1880,19 +1880,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>28900</v>
+        <v>28700</v>
       </c>
       <c r="E45" s="3">
-        <v>49200</v>
+        <v>48900</v>
       </c>
       <c r="F45" s="3">
-        <v>35600</v>
+        <v>35400</v>
       </c>
       <c r="G45" s="3">
-        <v>18200</v>
+        <v>18000</v>
       </c>
       <c r="H45" s="3">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="I45" s="3">
         <v>9700</v>
@@ -1916,22 +1916,22 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>885700</v>
+        <v>879700</v>
       </c>
       <c r="E46" s="3">
-        <v>1185000</v>
+        <v>1176900</v>
       </c>
       <c r="F46" s="3">
-        <v>1232800</v>
+        <v>1224400</v>
       </c>
       <c r="G46" s="3">
-        <v>1313100</v>
+        <v>1304200</v>
       </c>
       <c r="H46" s="3">
-        <v>330400</v>
+        <v>328200</v>
       </c>
       <c r="I46" s="3">
-        <v>423200</v>
+        <v>420300</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
@@ -1952,7 +1952,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="E47" s="3">
         <v>5800</v>
@@ -1961,13 +1961,13 @@
         <v>0</v>
       </c>
       <c r="G47" s="3">
-        <v>213900</v>
+        <v>212500</v>
       </c>
       <c r="H47" s="3">
-        <v>107700</v>
+        <v>107000</v>
       </c>
       <c r="I47" s="3">
-        <v>104400</v>
+        <v>103700</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
@@ -1988,19 +1988,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>16300</v>
+        <v>16200</v>
       </c>
       <c r="E48" s="3">
-        <v>55500</v>
+        <v>55100</v>
       </c>
       <c r="F48" s="3">
-        <v>54000</v>
+        <v>53600</v>
       </c>
       <c r="G48" s="3">
-        <v>55200</v>
+        <v>54800</v>
       </c>
       <c r="H48" s="3">
-        <v>52000</v>
+        <v>51700</v>
       </c>
       <c r="I48" s="3">
         <v>3800</v>
@@ -2024,22 +2024,22 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1290900</v>
+        <v>1282100</v>
       </c>
       <c r="E49" s="3">
-        <v>1352300</v>
+        <v>1343100</v>
       </c>
       <c r="F49" s="3">
-        <v>1277300</v>
+        <v>1268600</v>
       </c>
       <c r="G49" s="3">
-        <v>77200</v>
+        <v>76700</v>
       </c>
       <c r="H49" s="3">
-        <v>48700</v>
+        <v>48400</v>
       </c>
       <c r="I49" s="3">
-        <v>51500</v>
+        <v>51200</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -2132,16 +2132,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8000</v>
+        <v>7900</v>
       </c>
       <c r="E52" s="3">
-        <v>9500</v>
+        <v>9400</v>
       </c>
       <c r="F52" s="3">
-        <v>217400</v>
+        <v>215900</v>
       </c>
       <c r="G52" s="3">
-        <v>146200</v>
+        <v>145200</v>
       </c>
       <c r="H52" s="3">
         <v>1200</v>
@@ -2204,22 +2204,22 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2204800</v>
+        <v>2189800</v>
       </c>
       <c r="E54" s="3">
-        <v>2608100</v>
+        <v>2590400</v>
       </c>
       <c r="F54" s="3">
-        <v>2781500</v>
+        <v>2762500</v>
       </c>
       <c r="G54" s="3">
-        <v>1805700</v>
+        <v>1793400</v>
       </c>
       <c r="H54" s="3">
-        <v>540200</v>
+        <v>536500</v>
       </c>
       <c r="I54" s="3">
-        <v>586200</v>
+        <v>582200</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
@@ -2272,22 +2272,22 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>30900</v>
+        <v>30700</v>
       </c>
       <c r="E57" s="3">
-        <v>42000</v>
+        <v>41700</v>
       </c>
       <c r="F57" s="3">
-        <v>80300</v>
+        <v>79700</v>
       </c>
       <c r="G57" s="3">
-        <v>52000</v>
+        <v>51700</v>
       </c>
       <c r="H57" s="3">
-        <v>12000</v>
+        <v>11900</v>
       </c>
       <c r="I57" s="3">
-        <v>8100</v>
+        <v>8000</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -2320,7 +2320,7 @@
         <v>3800</v>
       </c>
       <c r="H58" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2344,22 +2344,22 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>251000</v>
+        <v>249300</v>
       </c>
       <c r="E59" s="3">
-        <v>250500</v>
+        <v>248800</v>
       </c>
       <c r="F59" s="3">
-        <v>225300</v>
+        <v>223800</v>
       </c>
       <c r="G59" s="3">
-        <v>162300</v>
+        <v>161200</v>
       </c>
       <c r="H59" s="3">
-        <v>52200</v>
+        <v>51900</v>
       </c>
       <c r="I59" s="3">
-        <v>41900</v>
+        <v>41600</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2380,22 +2380,22 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>287600</v>
+        <v>285600</v>
       </c>
       <c r="E60" s="3">
-        <v>302900</v>
+        <v>300800</v>
       </c>
       <c r="F60" s="3">
-        <v>309600</v>
+        <v>307500</v>
       </c>
       <c r="G60" s="3">
-        <v>218100</v>
+        <v>216600</v>
       </c>
       <c r="H60" s="3">
-        <v>67000</v>
+        <v>66500</v>
       </c>
       <c r="I60" s="3">
-        <v>50000</v>
+        <v>49600</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
@@ -2416,19 +2416,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>275100</v>
+        <v>273200</v>
       </c>
       <c r="E61" s="3">
-        <v>358900</v>
+        <v>356500</v>
       </c>
       <c r="F61" s="3">
-        <v>350500</v>
+        <v>348100</v>
       </c>
       <c r="G61" s="3">
-        <v>342500</v>
+        <v>340100</v>
       </c>
       <c r="H61" s="3">
-        <v>43600</v>
+        <v>43300</v>
       </c>
       <c r="I61" s="3">
         <v>100</v>
@@ -2452,19 +2452,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1588800</v>
+        <v>1578000</v>
       </c>
       <c r="E62" s="3">
-        <v>1775000</v>
+        <v>1763000</v>
       </c>
       <c r="F62" s="3">
-        <v>1854900</v>
+        <v>1842300</v>
       </c>
       <c r="G62" s="3">
-        <v>569100</v>
+        <v>565200</v>
       </c>
       <c r="H62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>4800</v>
@@ -2596,22 +2596,22 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2151500</v>
+        <v>2136800</v>
       </c>
       <c r="E66" s="3">
-        <v>2436800</v>
+        <v>2420300</v>
       </c>
       <c r="F66" s="3">
-        <v>2515000</v>
+        <v>2497900</v>
       </c>
       <c r="G66" s="3">
-        <v>1129700</v>
+        <v>1122000</v>
       </c>
       <c r="H66" s="3">
-        <v>110700</v>
+        <v>109900</v>
       </c>
       <c r="I66" s="3">
-        <v>54800</v>
+        <v>54500</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2792,22 +2792,22 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1102400</v>
+        <v>-1094900</v>
       </c>
       <c r="E72" s="3">
-        <v>-895900</v>
+        <v>-889900</v>
       </c>
       <c r="F72" s="3">
-        <v>-731600</v>
+        <v>-726600</v>
       </c>
       <c r="G72" s="3">
-        <v>-171800</v>
+        <v>-170600</v>
       </c>
       <c r="H72" s="3">
-        <v>-278300</v>
+        <v>-276400</v>
       </c>
       <c r="I72" s="3">
-        <v>-166200</v>
+        <v>-165100</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2936,22 +2936,22 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>53400</v>
+        <v>53000</v>
       </c>
       <c r="E76" s="3">
-        <v>171300</v>
+        <v>170100</v>
       </c>
       <c r="F76" s="3">
-        <v>266400</v>
+        <v>264600</v>
       </c>
       <c r="G76" s="3">
-        <v>676100</v>
+        <v>671500</v>
       </c>
       <c r="H76" s="3">
-        <v>429500</v>
+        <v>426600</v>
       </c>
       <c r="I76" s="3">
-        <v>531400</v>
+        <v>527800</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -3049,22 +3049,22 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-206400</v>
+        <v>-205000</v>
       </c>
       <c r="E81" s="3">
-        <v>-164400</v>
+        <v>-163200</v>
       </c>
       <c r="F81" s="3">
-        <v>-559800</v>
+        <v>-556000</v>
       </c>
       <c r="G81" s="3">
-        <v>106500</v>
+        <v>105800</v>
       </c>
       <c r="H81" s="3">
-        <v>-112100</v>
+        <v>-111300</v>
       </c>
       <c r="I81" s="3">
-        <v>-61100</v>
+        <v>-60700</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
@@ -3101,19 +3101,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="E83" s="3">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="F83" s="3">
-        <v>11000</v>
+        <v>10900</v>
       </c>
       <c r="G83" s="3">
-        <v>9100</v>
+        <v>9000</v>
       </c>
       <c r="H83" s="3">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="I83" s="3">
         <v>4100</v>
@@ -3317,22 +3317,22 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-321900</v>
+        <v>-319700</v>
       </c>
       <c r="E89" s="3">
-        <v>-399000</v>
+        <v>-396300</v>
       </c>
       <c r="F89" s="3">
-        <v>-523900</v>
+        <v>-520300</v>
       </c>
       <c r="G89" s="3">
-        <v>37600</v>
+        <v>37300</v>
       </c>
       <c r="H89" s="3">
-        <v>-88200</v>
+        <v>-87600</v>
       </c>
       <c r="I89" s="3">
-        <v>-35700</v>
+        <v>-35400</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -3477,22 +3477,22 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>16700</v>
+        <v>16600</v>
       </c>
       <c r="E94" s="3">
-        <v>375400</v>
+        <v>372800</v>
       </c>
       <c r="F94" s="3">
-        <v>-904200</v>
+        <v>-898100</v>
       </c>
       <c r="G94" s="3">
-        <v>-957100</v>
+        <v>-950600</v>
       </c>
       <c r="H94" s="3">
-        <v>86500</v>
+        <v>85900</v>
       </c>
       <c r="I94" s="3">
-        <v>-193400</v>
+        <v>-192100</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
@@ -3673,22 +3673,22 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>46800</v>
+        <v>46500</v>
       </c>
       <c r="E100" s="3">
-        <v>338900</v>
+        <v>336500</v>
       </c>
       <c r="F100" s="3">
-        <v>1439500</v>
+        <v>1429700</v>
       </c>
       <c r="G100" s="3">
-        <v>987100</v>
+        <v>980400</v>
       </c>
       <c r="H100" s="3">
         <v>400</v>
       </c>
       <c r="I100" s="3">
-        <v>195300</v>
+        <v>193900</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
@@ -3745,22 +3745,22 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-265300</v>
+        <v>-263500</v>
       </c>
       <c r="E102" s="3">
-        <v>303700</v>
+        <v>301600</v>
       </c>
       <c r="F102" s="3">
-        <v>14600</v>
+        <v>14500</v>
       </c>
       <c r="G102" s="3">
-        <v>71200</v>
+        <v>70800</v>
       </c>
       <c r="H102" s="3">
         <v>-1200</v>
       </c>
       <c r="I102" s="3">
-        <v>-33900</v>
+        <v>-33600</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
